--- a/output/pdf_financials_xlsx/ENDR.xlsx
+++ b/output/pdf_financials_xlsx/ENDR.xlsx
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-1.621652</v>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-1.621652</v>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-1.621652</v>
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>1.069378</v>
+        <v>-1.069378</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>9.009178</v>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-1.621652</v>
@@ -2016,10 +2016,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-1.621652</v>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -5758,34 +5758,34 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.037865</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.38476</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.3843</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.712718</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.712718</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.085284</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.26088</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.26088</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.717288</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.740307</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -6342,10 +6342,10 @@
         </is>
       </c>
       <c r="B103" s="3" t="n">
-        <v>0</v>
+        <v>-0.003693</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.013703</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>0</v>
@@ -6357,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.001733</v>
       </c>
       <c r="H103" s="3" t="n">
         <v>0</v>
@@ -6507,10 +6507,10 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.005</v>
+        <v>0.001307</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.069881</v>
+        <v>0.056178</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.008224</v>
@@ -6522,7 +6522,7 @@
         <v>0.134622</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.39641</v>
+        <v>0.398143</v>
       </c>
       <c r="H106" s="3" t="n">
         <v>0.21773</v>
@@ -7188,31 +7188,31 @@
         <v>-0.453801</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>-0.386431</v>
+        <v>-0.379281</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.267182</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>2.081567</v>
+        <v>0.545119</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>5.514071</v>
+        <v>-1.421469</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-4.844222</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0.196311</v>
+        <v>-5.223156</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-2.617959</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-1.433573</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-1.326376</v>
       </c>
     </row>
     <row r="119">
@@ -13988,7 +13988,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -14814,7 +14818,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -15766,7 +15774,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -17006,7 +17018,11 @@
           <t>Share-based payment reserve (Note 5)</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -17192,7 +17208,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -19536,7 +19556,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -23688,7 +23712,11 @@
           <t>Advances on exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -26074,7 +26102,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -28566,7 +28598,11 @@
           <t>Decrease (increase) in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30280,7 +30316,11 @@
           <t>Increase in prepaids and deposits</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E237" s="5" t="n">
         <v>-0.003693</v>
       </c>
@@ -47804,10 +47844,10 @@
         </is>
       </c>
       <c r="E422" s="5" t="n">
-        <v>0.0058</v>
+        <v>-0.0058</v>
       </c>
       <c r="F422" s="5" t="n">
-        <v>0.192488</v>
+        <v>-0.192488</v>
       </c>
       <c r="G422" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ENDR.xlsx
+++ b/output/pdf_financials_xlsx/ENDR.xlsx
@@ -2312,49 +2312,49 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.391257</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.032114</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.01964</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.025556</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.012541</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.15543</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.101983</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.071174</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.537241</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.135986</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.737224</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>4.027104</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.487498</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.148243</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.087751</v>
       </c>
     </row>
     <row r="35">
@@ -2426,49 +2426,49 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.391257</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.032114</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.01964</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.025556</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.012541</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.15543</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.101983</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.071174</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.175</v>
+        <v>0.712241</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.135986</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.737224</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>4.027104</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.487498</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.148243</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0.083</v>
+        <v>3.170751</v>
       </c>
     </row>
     <row r="37">
@@ -3110,49 +3110,49 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.408653</v>
+        <v>0.017396</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.083114</v>
+        <v>0.051</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.02064</v>
+        <v>0.001</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.027289</v>
+        <v>0.001733</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.012541</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.15543</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.101983</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.077371</v>
+        <v>0.006197</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.630505</v>
+        <v>0.093264</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.15554</v>
+        <v>3.019554</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.04271</v>
+        <v>0.305486</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>4.442253</v>
+        <v>0.415149</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.600949</v>
+        <v>0.113451</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.327152</v>
+        <v>0.178909</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.350101</v>
+        <v>0.26235</v>
       </c>
     </row>
     <row r="49">
@@ -7533,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.110122</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.112052</v>
       </c>
       <c r="P124" s="3" t="n">
         <v>0</v>
@@ -7588,10 +7588,10 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.110122</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.112052</v>
       </c>
       <c r="P125" s="3" t="n">
         <v>0</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -22964,7 +22964,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -31660,7 +31664,7 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -34746,7 +34750,7 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
